--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>145</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>6266</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>1452</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>0</v>
+        <v>1841</v>
       </c>
       <c r="C2715" t="n">
-        <v>4.09999990463257</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="D2715" t="n">
         <v>4.09999990463257</v>
       </c>
       <c r="E2715" t="n">
-        <v>4.09999990463257</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="F2715" t="n">
         <v>4.09999990463257</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C2716" t="n">
-        <v>4.15999984741211</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="D2716" t="n">
-        <v>4.15999984741211</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="E2716" t="n">
-        <v>4.15999984741211</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="F2716" t="n">
-        <v>4.15999984741211</v>
+        <v>4.09999990463257</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,10 +62842,10 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C2717" t="n">
         <v>4.15999984741211</v>
@@ -62865,13 +62865,13 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="C2718" t="n">
-        <v>4.23999977111816</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="D2718" t="n">
         <v>4.15999984741211</v>
@@ -62880,7 +62880,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="F2718" t="n">
-        <v>4.23999977111816</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>145</v>
+        <v>639</v>
       </c>
       <c r="C2719" t="n">
-        <v>4.30000019073486</v>
+        <v>4.23999977111816</v>
       </c>
       <c r="D2719" t="n">
-        <v>4.30000019073486</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="E2719" t="n">
-        <v>4.30000019073486</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="F2719" t="n">
-        <v>4.30000019073486</v>
+        <v>4.23999977111816</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>2250</v>
+        <v>145</v>
       </c>
       <c r="C2720" t="n">
-        <v>4.28000020980835</v>
+        <v>4.30000019073486</v>
       </c>
       <c r="D2720" t="n">
-        <v>4.11999988555908</v>
+        <v>4.30000019073486</v>
       </c>
       <c r="E2720" t="n">
-        <v>4.19999980926514</v>
+        <v>4.30000019073486</v>
       </c>
       <c r="F2720" t="n">
-        <v>4.28000020980835</v>
+        <v>4.30000019073486</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>6266</v>
+        <v>2250</v>
       </c>
       <c r="C2721" t="n">
-        <v>4.40000009536743</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="D2721" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F2721" t="n">
         <v>4.28000020980835</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>4.28000020980835</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>4.40000009536743</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>1452</v>
+        <v>6266</v>
       </c>
       <c r="C2722" t="n">
         <v>4.40000009536743</v>
       </c>
       <c r="D2722" t="n">
-        <v>4.40000009536743</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="E2722" t="n">
-        <v>4.40000009536743</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="F2722" t="n">
         <v>4.40000009536743</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>2849</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -62980,24 +62980,47 @@
     </row>
     <row r="2723">
       <c r="A2723" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1452</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B2723" t="n">
+      <c r="B2724" t="n">
         <v>2849</v>
       </c>
-      <c r="C2723" t="n">
+      <c r="C2724" t="n">
         <v>4.34000015258789</v>
       </c>
-      <c r="D2723" t="n">
+      <c r="D2724" t="n">
         <v>4.26000022888184</v>
       </c>
-      <c r="E2723" t="n">
+      <c r="E2724" t="n">
         <v>4.34000015258789</v>
       </c>
-      <c r="F2723" t="n">
+      <c r="F2724" t="n">
         <v>4.32000017166138</v>
       </c>
-      <c r="G2723" t="s">
+      <c r="G2724" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63116,6 +63116,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="F2730"/>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63155,7 +63155,9 @@
       <c r="E2730" t="n">
         <v>4.3600001335144</v>
       </c>
-      <c r="F2730"/>
+      <c r="F2730" t="n">
+        <v>4.3600001335144</v>
+      </c>
       <c r="G2730" t="s">
         <v>7</v>
       </c>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63162,6 +63162,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2731">
+      <c r="A2731" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2731" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2731" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2731" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="G2731" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63185,6 +63185,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="G2732" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2733" t="n">
+        <v>858</v>
+      </c>
+      <c r="C2733" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2733" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="F2733"/>
+      <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63254,6 +63254,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>3838</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63288,13 +63288,36 @@
         <v>4.28000020980835</v>
       </c>
       <c r="D2736" t="n">
-        <v>4.11999988555908</v>
+        <v>4.03999996185303</v>
       </c>
       <c r="E2736" t="n">
         <v>4.11999988555908</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>4.03999996185303</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1456</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>3.98000001907349</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>4.01999998092651</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>4.09999990463257</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63339,7 +63339,9 @@
       <c r="E2738" t="n">
         <v>4.09999990463257</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>4.07999992370605</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -63392,6 +63392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8710606098175</v>
+        <v>3.87105989456177</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>3.87458276748657</v>
+        <v>3.87458252906799</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8710606098175</v>
+        <v>3.87105989456177</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>3.87458276748657</v>
+        <v>3.87458252906799</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8657763004303</v>
+        <v>3.86577606201172</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8657763004303</v>
+        <v>3.86577606201172</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8657763004303</v>
+        <v>3.86577606201172</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>3.86401534080505</v>
+        <v>3.86401605606079</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G14" t="n">
-        <v>3.79532909393311</v>
+        <v>3.79532957077026</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>3.77771759033203</v>
+        <v>3.77771735191345</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G17" t="n">
-        <v>3.62977910041809</v>
+        <v>3.62977933883667</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.65443539619446</v>
+        <v>3.65443563461304</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>3.65443539619446</v>
+        <v>3.65443563461304</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G22" t="n">
-        <v>3.64386892318726</v>
+        <v>3.6438684463501</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>3.48712420463562</v>
+        <v>3.48712396621704</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G24" t="n">
-        <v>3.61040616035461</v>
+        <v>3.61040639877319</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G25" t="n">
-        <v>3.61040616035461</v>
+        <v>3.61040639877319</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G27" t="n">
-        <v>3.66676425933838</v>
+        <v>3.66676378250122</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G29" t="n">
-        <v>3.68085265159607</v>
+        <v>3.68085336685181</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>3.56637716293335</v>
+        <v>3.56637692451477</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>3.539959192276</v>
+        <v>3.53995943069458</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64915227890015</v>
+        <v>3.64915204048157</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G34" t="n">
-        <v>3.65267395973206</v>
+        <v>3.65267443656921</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65091276168823</v>
+        <v>3.65091300010681</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G36" t="n">
-        <v>3.65091276168823</v>
+        <v>3.65091300010681</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G37" t="n">
-        <v>3.65091276168823</v>
+        <v>3.65091300010681</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G38" t="n">
-        <v>3.65091276168823</v>
+        <v>3.65091300010681</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G39" t="n">
-        <v>3.65091276168823</v>
+        <v>3.65091300010681</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G40" t="n">
-        <v>3.65091276168823</v>
+        <v>3.65091300010681</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G41" t="n">
-        <v>3.64210724830627</v>
+        <v>3.64210748672485</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>3.65443539619446</v>
+        <v>3.65443563461304</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>3.8129415512085</v>
+        <v>3.81294107437134</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>3.87458276748657</v>
+        <v>3.87458252906799</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G49" t="n">
-        <v>3.79356861114502</v>
+        <v>3.79356813430786</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.87458276748657</v>
+        <v>3.87458252906799</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G51" t="n">
-        <v>3.86225390434265</v>
+        <v>3.86225414276123</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G52" t="n">
-        <v>3.87458276748657</v>
+        <v>3.87458252906799</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G53" t="n">
-        <v>3.86225390434265</v>
+        <v>3.86225414276123</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G55" t="n">
-        <v>3.81470203399658</v>
+        <v>3.81470251083374</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G56" t="n">
-        <v>3.80941915512085</v>
+        <v>3.80941963195801</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G57" t="n">
-        <v>3.73368835449219</v>
+        <v>3.73368811607361</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G58" t="n">
-        <v>3.73721051216125</v>
+        <v>3.73721075057983</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G60" t="n">
-        <v>3.73192763328552</v>
+        <v>3.73192715644836</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G61" t="n">
-        <v>3.72136044502258</v>
+        <v>3.72135996818542</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.76891183853149</v>
+        <v>3.76891231536865</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>3.76538920402527</v>
+        <v>3.76538944244385</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G64" t="n">
-        <v>3.74953866004944</v>
+        <v>3.74953889846802</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G65" t="n">
-        <v>3.74601674079895</v>
+        <v>3.74601650238037</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G66" t="n">
-        <v>3.74953866004944</v>
+        <v>3.74953889846802</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>3.73721051216125</v>
+        <v>3.73721075057983</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G68" t="n">
-        <v>3.73016548156738</v>
+        <v>3.7301664352417</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G69" t="n">
-        <v>3.6984646320343</v>
+        <v>3.69846439361572</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G71" t="n">
-        <v>3.68085265159607</v>
+        <v>3.68085336685181</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G73" t="n">
-        <v>3.72488284111023</v>
+        <v>3.72488260269165</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G74" t="n">
-        <v>3.76538920402527</v>
+        <v>3.76538944244385</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G77" t="n">
-        <v>3.8657763004303</v>
+        <v>3.86577606201172</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.87458276748657</v>
+        <v>3.87458252906799</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>3.95383453369141</v>
+        <v>3.95383501052856</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.9186110496521</v>
+        <v>3.91861081123352</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G81" t="n">
-        <v>3.93446183204651</v>
+        <v>3.93446278572083</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G82" t="n">
-        <v>3.98377537727356</v>
+        <v>3.98377466201782</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G83" t="n">
-        <v>3.94326853752136</v>
+        <v>3.94326829910278</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G84" t="n">
-        <v>3.91508913040161</v>
+        <v>3.91508889198303</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G86" t="n">
-        <v>3.98377537727356</v>
+        <v>3.98377466201782</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G88" t="n">
-        <v>3.89395546913147</v>
+        <v>3.89395475387573</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>3.9186110496521</v>
+        <v>3.91861081123352</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G90" t="n">
-        <v>3.94326853752136</v>
+        <v>3.94326829910278</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G91" t="n">
-        <v>3.9608793258667</v>
+        <v>3.96087956428528</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G92" t="n">
-        <v>3.9186110496521</v>
+        <v>3.91861081123352</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93446183204651</v>
+        <v>3.93446278572083</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>3.92741775512695</v>
+        <v>3.92741751670837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88338851928711</v>
+        <v>3.88338756561279</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G99" t="n">
-        <v>3.93446183204651</v>
+        <v>3.93446278572083</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G100" t="n">
-        <v>3.99916744232178</v>
+        <v>3.99916791915894</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>4.0261287689209</v>
+        <v>4.02612829208374</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>3.97220706939697</v>
+        <v>3.97220730781555</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G103" t="n">
-        <v>3.99018144607544</v>
+        <v>3.99018120765686</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G106" t="n">
-        <v>3.98299145698547</v>
+        <v>3.98299193382263</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>3.9542338848114</v>
+        <v>3.95423412322998</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>3.9542338848114</v>
+        <v>3.95423412322998</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G110" t="n">
-        <v>3.88233828544617</v>
+        <v>3.88233804702759</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G111" t="n">
-        <v>3.92727279663086</v>
+        <v>3.92727303504944</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G112" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G113" t="n">
-        <v>3.9236786365509</v>
+        <v>3.92367839813232</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G123" t="n">
-        <v>3.70799279212952</v>
+        <v>3.70799231529236</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>3.59475779533386</v>
+        <v>3.59475803375244</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G126" t="n">
-        <v>3.61273145675659</v>
+        <v>3.61273169517517</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>3.63070511817932</v>
+        <v>3.63070487976074</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="G132" t="n">
-        <v>3.59475779533386</v>
+        <v>3.59475803375244</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G135" t="n">
-        <v>3.57318925857544</v>
+        <v>3.57318949699402</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G136" t="n">
-        <v>3.61632633209229</v>
+        <v>3.61632657051086</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G137" t="n">
-        <v>3.60374474525452</v>
+        <v>3.6037449836731</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G138" t="n">
-        <v>3.60374474525452</v>
+        <v>3.6037449836731</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G139" t="n">
-        <v>3.64688181877136</v>
+        <v>3.64688205718994</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G140" t="n">
-        <v>3.69181609153748</v>
+        <v>3.6918158531189</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G141" t="n">
-        <v>3.73675084114075</v>
+        <v>3.73675060272217</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G142" t="n">
-        <v>3.75652122497559</v>
+        <v>3.75652146339417</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G143" t="n">
-        <v>3.8032534122467</v>
+        <v>3.80325365066528</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G155" t="n">
-        <v>3.81763291358948</v>
+        <v>3.8176326751709</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G156" t="n">
-        <v>3.81763291358948</v>
+        <v>3.8176326751709</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G162" t="n">
-        <v>3.7439398765564</v>
+        <v>3.74394011497498</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G163" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G164" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G165" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G166" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G171" t="n">
-        <v>3.79067182540894</v>
+        <v>3.79067230224609</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G175" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G176" t="n">
-        <v>3.77629280090332</v>
+        <v>3.7762930393219</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G177" t="n">
-        <v>3.77629280090332</v>
+        <v>3.7762930393219</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G179" t="n">
-        <v>3.79067182540894</v>
+        <v>3.79067230224609</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G180" t="n">
-        <v>3.79067182540894</v>
+        <v>3.79067230224609</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G182" t="n">
-        <v>3.78887438774109</v>
+        <v>3.78887462615967</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>3.74753499031067</v>
+        <v>3.74753522872925</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G187" t="n">
-        <v>3.75112962722778</v>
+        <v>3.7511293888092</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G188" t="n">
-        <v>3.75112962722778</v>
+        <v>3.7511293888092</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G189" t="n">
-        <v>3.74753499031067</v>
+        <v>3.74753522872925</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>3.78348231315613</v>
+        <v>3.78348255157471</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>3.78348231315613</v>
+        <v>3.78348255157471</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G197" t="n">
-        <v>3.72416925430298</v>
+        <v>3.7241690158844</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G198" t="n">
-        <v>3.72416925430298</v>
+        <v>3.7241690158844</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G199" t="n">
-        <v>3.77090096473694</v>
+        <v>3.77090120315552</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G200" t="n">
-        <v>3.75652122497559</v>
+        <v>3.75652146339417</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G201" t="n">
-        <v>3.73675084114075</v>
+        <v>3.73675060272217</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G202" t="n">
-        <v>3.70799279212952</v>
+        <v>3.70799231529236</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>3.72057390213013</v>
+        <v>3.72057437896729</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G204" t="n">
-        <v>3.76371145248413</v>
+        <v>3.76371192932129</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>3.72596597671509</v>
+        <v>3.72596621513367</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G206" t="n">
-        <v>3.70978975296021</v>
+        <v>3.70978927612305</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G212" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.72956085205078</v>
+        <v>3.72956109046936</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G218" t="n">
-        <v>3.72776341438293</v>
+        <v>3.72776365280151</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>3.74753499031067</v>
+        <v>3.74753522872925</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G226" t="n">
-        <v>3.69541072845459</v>
+        <v>3.69541096687317</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G227" t="n">
-        <v>3.69541072845459</v>
+        <v>3.69541096687317</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G229" t="n">
-        <v>3.69361352920532</v>
+        <v>3.69361329078674</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G230" t="n">
-        <v>3.69541072845459</v>
+        <v>3.69541096687317</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>3.69361352920532</v>
+        <v>3.69361329078674</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G233" t="n">
-        <v>3.68822169303894</v>
+        <v>3.68822145462036</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>3.72956085205078</v>
+        <v>3.72956109046936</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G237" t="n">
-        <v>3.73135852813721</v>
+        <v>3.73135876655579</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G240" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>3.77449536323547</v>
+        <v>3.77449560165405</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.21799993515015</v>
       </c>
       <c r="G242" t="n">
-        <v>3.79067182540894</v>
+        <v>3.79067230224609</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G244" t="n">
-        <v>3.8338086605072</v>
+        <v>3.83380913734436</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G245" t="n">
-        <v>3.77629280090332</v>
+        <v>3.7762930393219</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G246" t="n">
-        <v>3.81224036216736</v>
+        <v>3.81224060058594</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G247" t="n">
-        <v>3.81583499908447</v>
+        <v>3.81583523750305</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G248" t="n">
-        <v>3.81763291358948</v>
+        <v>3.8176326751709</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G249" t="n">
-        <v>3.81763291358948</v>
+        <v>3.8176326751709</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G250" t="n">
-        <v>3.81763291358948</v>
+        <v>3.8176326751709</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G252" t="n">
-        <v>3.82661938667297</v>
+        <v>3.82661962509155</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82841753959656</v>
+        <v>3.82841730117798</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G256" t="n">
-        <v>3.92547535896301</v>
+        <v>3.92547512054443</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="n">
-        <v>3.93446207046509</v>
+        <v>3.93446278572083</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G258" t="n">
-        <v>3.92547535896301</v>
+        <v>3.92547512054443</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="n">
-        <v>3.92188048362732</v>
+        <v>3.9218807220459</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="n">
-        <v>3.90031266212463</v>
+        <v>3.90031218528748</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="n">
-        <v>3.87335109710693</v>
+        <v>3.87335133552551</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>3.87335109710693</v>
+        <v>3.87335133552551</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.87335109710693</v>
+        <v>3.87335133552551</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="n">
-        <v>3.87335109710693</v>
+        <v>3.87335133552551</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="n">
-        <v>3.87335109710693</v>
+        <v>3.87335133552551</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>3.87335109710693</v>
+        <v>3.87335133552551</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="n">
-        <v>3.84639096260071</v>
+        <v>3.84639072418213</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.83740425109863</v>
+        <v>3.83740401268005</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G271" t="n">
-        <v>3.92727279663086</v>
+        <v>3.92727303504944</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G272" t="n">
-        <v>3.92727279663086</v>
+        <v>3.92727303504944</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="n">
-        <v>3.9416515827179</v>
+        <v>3.94165182113647</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G275" t="n">
-        <v>3.92727279663086</v>
+        <v>3.92727303504944</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>3.90929889678955</v>
+        <v>3.90929913520813</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="n">
-        <v>3.92188048362732</v>
+        <v>3.9218807220459</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>3.9542338848114</v>
+        <v>3.95423412322998</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>3.9542338848114</v>
+        <v>3.95423412322998</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="n">
-        <v>3.88413572311401</v>
+        <v>3.88413596153259</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>3.88413572311401</v>
+        <v>3.88413596153259</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G285" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="n">
-        <v>3.94884133338928</v>
+        <v>3.94884157180786</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="n">
-        <v>3.87874293327332</v>
+        <v>3.87874317169189</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G291" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>4.02073669433594</v>
+        <v>4.02073621749878</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G294" t="n">
-        <v>3.9542338848114</v>
+        <v>3.95423412322998</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>4.00815486907959</v>
+        <v>4.00815439224243</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G296" t="n">
-        <v>3.99916744232178</v>
+        <v>3.99916791915894</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>3.99916744232178</v>
+        <v>3.99916791915894</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="n">
-        <v>4.05308961868286</v>
+        <v>4.0530891418457</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.5</v>
       </c>
       <c r="G301" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>4.00815486907959</v>
+        <v>4.00815439224243</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>4.0261287689209</v>
+        <v>4.02612829208374</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="n">
-        <v>4.01714181900024</v>
+        <v>4.01714134216309</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="n">
-        <v>4.06207609176636</v>
+        <v>4.0620756149292</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.5</v>
       </c>
       <c r="G306" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.5</v>
       </c>
       <c r="G307" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.06207609176636</v>
+        <v>4.0620756149292</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.5</v>
       </c>
       <c r="G309" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.5</v>
       </c>
       <c r="G310" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="n">
-        <v>4.14295864105225</v>
+        <v>4.14295816421509</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>4.08903646469116</v>
+        <v>4.08903741836548</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="n">
-        <v>4.37661695480347</v>
+        <v>4.37661790847778</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="n">
-        <v>4.34785938262939</v>
+        <v>4.34785890579224</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>4.32808876037598</v>
+        <v>4.32808828353882</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.11599731445312</v>
+        <v>4.11599779129028</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.5</v>
       </c>
       <c r="G324" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="n">
-        <v>3.98478865623474</v>
+        <v>3.9847891330719</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="n">
-        <v>4.04230499267578</v>
+        <v>4.04230451583862</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.5</v>
       </c>
       <c r="G329" t="n">
-        <v>4.04410219192505</v>
+        <v>4.04410171508789</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>4.0261287689209</v>
+        <v>4.02612829208374</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>3.97220706939697</v>
+        <v>3.97220730781555</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G332" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="n">
-        <v>3.95603060722351</v>
+        <v>3.95603132247925</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="n">
-        <v>3.92008304595947</v>
+        <v>3.92008376121521</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="n">
-        <v>3.91828584671021</v>
+        <v>3.91828608512878</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G336" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G337" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.9542338848114</v>
+        <v>3.95423412322998</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="n">
-        <v>3.94704461097717</v>
+        <v>3.94704413414001</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="n">
-        <v>3.93266463279724</v>
+        <v>3.9326651096344</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.90031266212463</v>
+        <v>3.90031218528748</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="n">
-        <v>3.86795949935913</v>
+        <v>3.86795902252197</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G347" t="n">
-        <v>3.88233828544617</v>
+        <v>3.88233804702759</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G349" t="n">
-        <v>3.86436486244202</v>
+        <v>3.86436462402344</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G350" t="n">
-        <v>3.92547535896301</v>
+        <v>3.92547512054443</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>3.93625974655151</v>
+        <v>3.93625998497009</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.90929889678955</v>
+        <v>3.90929913520813</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="n">
-        <v>3.90390706062317</v>
+        <v>3.90390634536743</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>4.06819152832031</v>
+        <v>4.06819105148315</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>3.89019656181335</v>
+        <v>3.89019632339478</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G361" t="n">
-        <v>3.87184619903564</v>
+        <v>3.87184643745422</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G367" t="n">
-        <v>4.10672664642334</v>
+        <v>4.10672616958618</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G381" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>4.05534648895264</v>
+        <v>4.05534601211548</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G390" t="n">
-        <v>4.09021186828613</v>
+        <v>4.09021139144897</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G391" t="n">
-        <v>4.09021186828613</v>
+        <v>4.09021139144897</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>4.16544675827026</v>
+        <v>4.16544628143311</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G401" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G402" t="n">
-        <v>4.09388160705566</v>
+        <v>4.09388113021851</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>4.09388160705566</v>
+        <v>4.09388113021851</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G404" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>4.16544675827026</v>
+        <v>4.16544628143311</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G406" t="n">
-        <v>4.20948648452759</v>
+        <v>4.20948600769043</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G408" t="n">
-        <v>4.13792181015015</v>
+        <v>4.13792133331299</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G410" t="n">
-        <v>4.12507629394531</v>
+        <v>4.12507677078247</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G421" t="n">
-        <v>4.17278623580933</v>
+        <v>4.17278575897217</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G425" t="n">
-        <v>4.07002639770508</v>
+        <v>4.07002592086792</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G426" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.10122156143188</v>
+        <v>4.10122203826904</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G430" t="n">
-        <v>4.16911649703979</v>
+        <v>4.16911697387695</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>4.13792181015015</v>
+        <v>4.13792133331299</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>4.16544675827026</v>
+        <v>4.16544628143311</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G435" t="n">
-        <v>4.16544675827026</v>
+        <v>4.16544628143311</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G437" t="n">
-        <v>4.17278623580933</v>
+        <v>4.17278575897217</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G438" t="n">
-        <v>4.17278623580933</v>
+        <v>4.17278575897217</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>4.21132183074951</v>
+        <v>4.21132135391235</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G444" t="n">
-        <v>4.10122156143188</v>
+        <v>4.10122203826904</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G445" t="n">
-        <v>4.07920169830322</v>
+        <v>4.07920122146606</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G446" t="n">
-        <v>4.13425159454346</v>
+        <v>4.1342511177063</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G448" t="n">
-        <v>4.21866178512573</v>
+        <v>4.21866130828857</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G451" t="n">
-        <v>4.12140703201294</v>
+        <v>4.12140655517578</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G452" t="n">
-        <v>4.11590147018433</v>
+        <v>4.11590194702148</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G456" t="n">
-        <v>4.12140703201294</v>
+        <v>4.12140655517578</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G457" t="n">
-        <v>4.12140703201294</v>
+        <v>4.12140655517578</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>4.11773633956909</v>
+        <v>4.11773586273193</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>4.16544675827026</v>
+        <v>4.16544628143311</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G474" t="n">
-        <v>4.21866178512573</v>
+        <v>4.21866130828857</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G478" t="n">
-        <v>4.19297170639038</v>
+        <v>4.19297218322754</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G480" t="n">
-        <v>4.10122156143188</v>
+        <v>4.10122203826904</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G482" t="n">
-        <v>3.99662637710571</v>
+        <v>3.99662661552429</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G483" t="n">
-        <v>3.99662637710571</v>
+        <v>3.99662661552429</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G485" t="n">
-        <v>3.9856162071228</v>
+        <v>3.98561644554138</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G487" t="n">
-        <v>3.94341135025024</v>
+        <v>3.94341087341309</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G489" t="n">
-        <v>3.99662637710571</v>
+        <v>3.99662661552429</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G490" t="n">
-        <v>4.07920169830322</v>
+        <v>4.07920122146606</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>4.0204815864563</v>
+        <v>4.02048110961914</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>4.08654117584229</v>
+        <v>4.08654165267944</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G500" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>3.96726655960083</v>
+        <v>3.96726632118225</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G503" t="n">
-        <v>3.92506170272827</v>
+        <v>3.92506122589111</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G509" t="n">
-        <v>3.93790674209595</v>
+        <v>3.93790626525879</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G510" t="n">
-        <v>3.99846124649048</v>
+        <v>3.99846196174622</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>4.05534648895264</v>
+        <v>4.05534601211548</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>3.88102173805237</v>
+        <v>3.88102149963379</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>3.85349655151367</v>
+        <v>3.85349678993225</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G543" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G544" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G548" t="n">
-        <v>3.89019656181335</v>
+        <v>3.89019632339478</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G553" t="n">
-        <v>3.88102173805237</v>
+        <v>3.88102149963379</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G555" t="n">
-        <v>3.83514642715454</v>
+        <v>3.83514618873596</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G556" t="n">
-        <v>3.89019656181335</v>
+        <v>3.89019632339478</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.25</v>
       </c>
       <c r="G558" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G559" t="n">
-        <v>3.83514642715454</v>
+        <v>3.83514618873596</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>3.85349655151367</v>
+        <v>3.85349678993225</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.25</v>
       </c>
       <c r="G563" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>3.88102173805237</v>
+        <v>3.88102149963379</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>3.86267161369324</v>
+        <v>3.86267185211182</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>3.86267161369324</v>
+        <v>3.86267185211182</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>3.86267161369324</v>
+        <v>3.86267185211182</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G575" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G576" t="n">
-        <v>3.87184619903564</v>
+        <v>3.87184643745422</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G579" t="n">
-        <v>3.86267161369324</v>
+        <v>3.86267185211182</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G589" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>4.08287143707275</v>
+        <v>4.0828709602356</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>4.05534648895264</v>
+        <v>4.05534601211548</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>4.05534648895264</v>
+        <v>4.05534601211548</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>3.88102173805237</v>
+        <v>3.88102149963379</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>3.78927206993103</v>
+        <v>3.78927183151245</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.80762147903442</v>
+        <v>3.807621717453</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G616" t="n">
-        <v>3.89019656181335</v>
+        <v>3.89019632339478</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>3.85349655151367</v>
+        <v>3.85349678993225</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>3.85349655151367</v>
+        <v>3.85349678993225</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>3.85349655151367</v>
+        <v>3.85349678993225</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G625" t="n">
-        <v>3.87184619903564</v>
+        <v>3.87184643745422</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G637" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G638" t="n">
-        <v>4.10122156143188</v>
+        <v>4.10122203826904</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>4.11039638519287</v>
+        <v>4.11039590835571</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>4.05534648895264</v>
+        <v>4.05534601211548</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="n">
-        <v>3.98194646835327</v>
+        <v>3.98194670677185</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.25</v>
       </c>
       <c r="G655" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.25</v>
       </c>
       <c r="G667" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.25</v>
       </c>
       <c r="G668" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.25</v>
       </c>
       <c r="G669" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.25</v>
       </c>
       <c r="G670" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.25</v>
       </c>
       <c r="G671" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G672" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="n">
-        <v>3.96359634399414</v>
+        <v>3.96359658241272</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G679" t="n">
-        <v>3.97277164459229</v>
+        <v>3.97277140617371</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.25</v>
       </c>
       <c r="G682" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>3.91772174835205</v>
+        <v>3.91772150993347</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>3.78927206993103</v>
+        <v>3.78927183151245</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G688" t="n">
-        <v>3.87184619903564</v>
+        <v>3.87184643745422</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G689" t="n">
-        <v>3.87184619903564</v>
+        <v>3.87184643745422</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.25</v>
       </c>
       <c r="G691" t="n">
-        <v>3.89937162399292</v>
+        <v>3.89937138557434</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>3.94524645805359</v>
+        <v>3.94524693489075</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G698" t="n">
-        <v>4.04857492446899</v>
+        <v>4.04857444763184</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G700" t="n">
-        <v>4.04857492446899</v>
+        <v>4.04857444763184</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>3.97342705726624</v>
+        <v>3.97342729568481</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>3.97342705726624</v>
+        <v>3.97342729568481</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G703" t="n">
-        <v>3.97342705726624</v>
+        <v>3.97342729568481</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.25</v>
       </c>
       <c r="G704" t="n">
-        <v>3.9922137260437</v>
+        <v>3.99221396446228</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>4.02978754043579</v>
+        <v>4.02978801727295</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.25</v>
       </c>
       <c r="G706" t="n">
-        <v>3.9922137260437</v>
+        <v>3.99221396446228</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G707" t="n">
-        <v>3.96403360366821</v>
+        <v>3.96403288841248</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>3.9170663356781</v>
+        <v>3.91706609725952</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>3.77616453170776</v>
+        <v>3.77616477012634</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.70101690292358</v>
+        <v>3.70101714134216</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G713" t="n">
-        <v>3.73859095573425</v>
+        <v>3.73859071731567</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>3.71980428695679</v>
+        <v>3.71980381011963</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>3.63526272773743</v>
+        <v>3.63526296615601</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G717" t="n">
-        <v>3.62586951255798</v>
+        <v>3.6258692741394</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>3.35345983505249</v>
+        <v>3.35345935821533</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>3.33467292785645</v>
+        <v>3.33467268943787</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G724" t="n">
-        <v>3.37224626541138</v>
+        <v>3.37224650382996</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>3.46618103981018</v>
+        <v>3.4661808013916</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>3.44739437103271</v>
+        <v>3.44739413261414</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G755" t="n">
-        <v>3.35345983505249</v>
+        <v>3.35345935821533</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G756" t="n">
-        <v>3.31588554382324</v>
+        <v>3.31588578224182</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G758" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>3.63526272773743</v>
+        <v>3.63526296615601</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>3.46618103981018</v>
+        <v>3.4661808013916</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>3.73859095573425</v>
+        <v>3.73859071731567</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G775" t="n">
-        <v>3.62586951255798</v>
+        <v>3.6258692741394</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G776" t="n">
-        <v>3.62586951255798</v>
+        <v>3.6258692741394</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G777" t="n">
-        <v>3.62586951255798</v>
+        <v>3.6258692741394</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G779" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G783" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G785" t="n">
-        <v>3.53193521499634</v>
+        <v>3.53193497657776</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G786" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G787" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G788" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G789" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G792" t="n">
-        <v>3.53193521499634</v>
+        <v>3.53193497657776</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G793" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G794" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G796" t="n">
-        <v>3.53193521499634</v>
+        <v>3.53193497657776</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G799" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G810" t="n">
-        <v>3.63526272773743</v>
+        <v>3.63526296615601</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G812" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G814" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G818" t="n">
-        <v>3.62586951255798</v>
+        <v>3.6258692741394</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G819" t="n">
-        <v>3.63526272773743</v>
+        <v>3.63526296615601</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G821" t="n">
-        <v>3.63526272773743</v>
+        <v>3.63526296615601</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>3.63526272773743</v>
+        <v>3.63526296615601</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G828" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>3.71980428695679</v>
+        <v>3.71980381011963</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>3.73859095573425</v>
+        <v>3.73859071731567</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G833" t="n">
-        <v>3.70101690292358</v>
+        <v>3.70101714134216</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G839" t="n">
-        <v>3.70101690292358</v>
+        <v>3.70101714134216</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G841" t="n">
-        <v>3.70101690292358</v>
+        <v>3.70101714134216</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G846" t="n">
-        <v>3.62586951255798</v>
+        <v>3.6258692741394</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G847" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G848" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G852" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G853" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G854" t="n">
-        <v>3.53193521499634</v>
+        <v>3.53193497657776</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G860" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G861" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G862" t="n">
-        <v>3.53193521499634</v>
+        <v>3.53193497657776</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>3.56950879096985</v>
+        <v>3.56950902938843</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G885" t="n">
-        <v>3.54921507835388</v>
+        <v>3.54921531677246</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>3.66495037078857</v>
+        <v>3.66495013237</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G894" t="n">
-        <v>3.74210715293884</v>
+        <v>3.74210739135742</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>3.8385534286499</v>
+        <v>3.83855295181274</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>3.8385534286499</v>
+        <v>3.83855295181274</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>3.8385534286499</v>
+        <v>3.83855295181274</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="n">
-        <v>3.74210715293884</v>
+        <v>3.74210739135742</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>3.66495037078857</v>
+        <v>3.66495013237</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G923" t="n">
-        <v>3.66495037078857</v>
+        <v>3.66495013237</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G924" t="n">
-        <v>3.66495037078857</v>
+        <v>3.66495013237</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G939" t="n">
-        <v>3.54921507835388</v>
+        <v>3.54921531677246</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G940" t="n">
-        <v>3.52992606163025</v>
+        <v>3.52992582321167</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G941" t="n">
-        <v>3.52992606163025</v>
+        <v>3.52992582321167</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G942" t="n">
-        <v>3.52992606163025</v>
+        <v>3.52992582321167</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G943" t="n">
-        <v>3.52992606163025</v>
+        <v>3.52992582321167</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>3.47205805778503</v>
+        <v>3.47205829620361</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G946" t="n">
-        <v>3.51063656806946</v>
+        <v>3.51063680648804</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>3.41419076919556</v>
+        <v>3.41419053077698</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G949" t="n">
-        <v>3.4527690410614</v>
+        <v>3.45276880264282</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.5</v>
       </c>
       <c r="G950" t="n">
-        <v>3.37561202049255</v>
+        <v>3.37561225891113</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.5</v>
       </c>
       <c r="G951" t="n">
-        <v>3.37561202049255</v>
+        <v>3.37561225891113</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G952" t="n">
-        <v>3.39490127563477</v>
+        <v>3.39490151405334</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G953" t="n">
-        <v>3.39490127563477</v>
+        <v>3.39490151405334</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G955" t="n">
-        <v>3.27916622161865</v>
+        <v>3.27916598320007</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G960" t="n">
-        <v>3.20200896263123</v>
+        <v>3.2020092010498</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G972" t="n">
-        <v>2.83551430702209</v>
+        <v>2.83551406860352</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.95124936103821</v>
+        <v>2.95124959945679</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.95124936103821</v>
+        <v>2.95124959945679</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.8162248134613</v>
+        <v>2.81622505187988</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.8162248134613</v>
+        <v>2.81622505187988</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.75835728645325</v>
+        <v>2.75835704803467</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.8162248134613</v>
+        <v>2.81622505187988</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.8162248134613</v>
+        <v>2.81622505187988</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.54617595672607</v>
+        <v>2.54617619514465</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.54617595672607</v>
+        <v>2.54617619514465</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.50759744644165</v>
+        <v>2.50759768486023</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.14110279083252</v>
+        <v>2.14110255241394</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.23754858970642</v>
+        <v>2.23754835128784</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.02536725997925</v>
+        <v>2.02536749839783</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.23754858970642</v>
+        <v>2.23754835128784</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26648235321045</v>
+        <v>2.26648259162903</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>2.5</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.41115164756775</v>
+        <v>2.41115140914917</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.43044066429138</v>
+        <v>2.43044090270996</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>2.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.41115164756775</v>
+        <v>2.41115140914917</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.24719333648682</v>
+        <v>2.24719309806824</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.26648235321045</v>
+        <v>2.26648259162903</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.35328412055969</v>
+        <v>2.35328388214111</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.32434988021851</v>
+        <v>2.32435011863708</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.26648235321045</v>
+        <v>2.26648259162903</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.26648235321045</v>
+        <v>2.26648259162903</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.26648235321045</v>
+        <v>2.26648259162903</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.23754858970642</v>
+        <v>2.23754835128784</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.24719333648682</v>
+        <v>2.24719309806824</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.23754858970642</v>
+        <v>2.23754835128784</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.17968082427979</v>
+        <v>2.17968106269836</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.17968082427979</v>
+        <v>2.17968106269836</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.14110279083252</v>
+        <v>2.14110255241394</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.1314582824707</v>
+        <v>2.13145804405212</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.11216878890991</v>
+        <v>2.11216855049133</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.03501176834106</v>
+        <v>2.03501152992249</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.92409896850586</v>
+        <v>1.92409884929657</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.93856573104858</v>
+        <v>1.93856585025787</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.95785510540009</v>
+        <v>1.9578549861908</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.02536725997925</v>
+        <v>2.02536749839783</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.14110279083252</v>
+        <v>2.14110255241394</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.17968082427979</v>
+        <v>2.17968106269836</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.17968082427979</v>
+        <v>2.17968106269836</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.23754858970642</v>
+        <v>2.23754835128784</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.24719333648682</v>
+        <v>2.24719309806824</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.24719333648682</v>
+        <v>2.24719309806824</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.23754858970642</v>
+        <v>2.23754835128784</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.17968082427979</v>
+        <v>2.17968106269836</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.15074729919434</v>
+        <v>2.15074706077576</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.15074729919434</v>
+        <v>2.15074706077576</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.18932557106018</v>
+        <v>2.18932580947876</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.15074729919434</v>
+        <v>2.15074706077576</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.32434988021851</v>
+        <v>2.32435011863708</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.35328412055969</v>
+        <v>2.35328388214111</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.32434988021851</v>
+        <v>2.32435011863708</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.26648235321045</v>
+        <v>2.26648259162903</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.32434988021851</v>
+        <v>2.32435011863708</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.29541611671448</v>
+        <v>2.29541635513306</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.27612709999084</v>
+        <v>2.27612686157227</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.28577160835266</v>
+        <v>2.28577136993408</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.30506086349487</v>
+        <v>2.30506110191345</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.35328412055969</v>
+        <v>2.35328388214111</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.38221788406372</v>
+        <v>2.38221764564514</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.66191148757935</v>
+        <v>2.66191124916077</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.64262223243713</v>
+        <v>2.64262199401855</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.61368823051453</v>
+        <v>2.61368846893311</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.54617595672607</v>
+        <v>2.54617619514465</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.54617595672607</v>
+        <v>2.54617619514465</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.52688694000244</v>
+        <v>2.52688670158386</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.54617595672607</v>
+        <v>2.54617619514465</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.70048952102661</v>
+        <v>2.70048975944519</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.71013402938843</v>
+        <v>2.71013450622559</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.70048952102661</v>
+        <v>2.70048975944519</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.70048952102661</v>
+        <v>2.70048975944519</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.66191148757935</v>
+        <v>2.66191124916077</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.6812002658844</v>
+        <v>2.68120050430298</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.70048952102661</v>
+        <v>2.70048975944519</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.70048952102661</v>
+        <v>2.70048975944519</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.71013402938843</v>
+        <v>2.71013450622559</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.72942352294922</v>
+        <v>2.72942328453064</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.72942352294922</v>
+        <v>2.72942328453064</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.78729128837585</v>
+        <v>2.78729152679443</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.96089386940002</v>
+        <v>2.9608941078186</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.16343092918396</v>
+        <v>3.16343069076538</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.21165347099304</v>
+        <v>3.21165370941162</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.21165347099304</v>
+        <v>3.21165370941162</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.16343092918396</v>
+        <v>3.16343069076538</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.20200896263123</v>
+        <v>3.2020092010498</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.20200896263123</v>
+        <v>3.2020092010498</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.20200896263123</v>
+        <v>3.2020092010498</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.16343092918396</v>
+        <v>3.16343069076538</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.16343092918396</v>
+        <v>3.16343069076538</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.20200896263123</v>
+        <v>3.2020092010498</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.26952147483826</v>
+        <v>3.26952171325684</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.26952147483826</v>
+        <v>3.26952171325684</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.17307543754578</v>
+        <v>3.1730751991272</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.16343092918396</v>
+        <v>3.16343069076538</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.30809998512268</v>
+        <v>3.30810022354126</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.32738924026489</v>
+        <v>3.32738900184631</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.27916622161865</v>
+        <v>3.27916598320007</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.27916622161865</v>
+        <v>3.27916598320007</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.27916622161865</v>
+        <v>3.27916598320007</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.27916622161865</v>
+        <v>3.27916598320007</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.25023221969604</v>
+        <v>3.25023198127747</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.09591841697693</v>
+        <v>3.09591865539551</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1407" t="n">
-        <v>2.96089386940002</v>
+        <v>2.9608941078186</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.96089386940002</v>
+        <v>2.9608941078186</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.96089386940002</v>
+        <v>2.9608941078186</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.96089386940002</v>
+        <v>2.9608941078186</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.93196034431458</v>
+        <v>2.931960105896</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.95124936103821</v>
+        <v>2.95124959945679</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.96089386940002</v>
+        <v>2.9608941078186</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.95124936103821</v>
+        <v>2.95124959945679</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.83551430702209</v>
+        <v>2.83551406860352</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.80658054351807</v>
+        <v>2.80658030509949</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.83551430702209</v>
+        <v>2.83551406860352</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.92231583595276</v>
+        <v>2.92231559753418</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.93196034431458</v>
+        <v>2.931960105896</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.98982763290405</v>
+        <v>2.98982787132263</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.03805112838745</v>
+        <v>3.03805088996887</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.09591841697693</v>
+        <v>3.09591865539551</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.09591841697693</v>
+        <v>3.09591865539551</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.09591841697693</v>
+        <v>3.09591865539551</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.16343092918396</v>
+        <v>3.16343069076538</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.20200896263123</v>
+        <v>3.2020092010498</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.23094296455383</v>
+        <v>3.23094320297241</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.26952147483826</v>
+        <v>3.26952171325684</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.41419076919556</v>
+        <v>3.41419053077698</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.74210715293884</v>
+        <v>3.74210739135742</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.74210715293884</v>
+        <v>3.74210739135742</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.79033017158508</v>
+        <v>3.79033041000366</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.79033017158508</v>
+        <v>3.79033041000366</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.9446439743042</v>
+        <v>3.94464373588562</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.98322248458862</v>
+        <v>3.9832227230072</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.0507345199585</v>
+        <v>4.05073499679565</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.0507345199585</v>
+        <v>4.05073499679565</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.9446439743042</v>
+        <v>3.94464373588562</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1544" t="n">
-        <v>4.07002353668213</v>
+        <v>4.07002305984497</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1546" t="n">
-        <v>4.26291656494141</v>
+        <v>4.26291608810425</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1547" t="n">
-        <v>4.30149459838867</v>
+        <v>4.30149412155151</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1549" t="n">
-        <v>4.34971761703491</v>
+        <v>4.34971714019775</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1552" t="n">
-        <v>4.42687463760376</v>
+        <v>4.4268741607666</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1554" t="n">
-        <v>4.22433757781982</v>
+        <v>4.22433710098267</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.03144502639771</v>
+        <v>4.03144550323486</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1560" t="n">
-        <v>4.40758562088013</v>
+        <v>4.40758514404297</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1562" t="n">
-        <v>4.5329647064209</v>
+        <v>4.53296518325806</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1564" t="n">
-        <v>4.3690071105957</v>
+        <v>4.36900663375854</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1567" t="n">
-        <v>4.25327110290527</v>
+        <v>4.25327157974243</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.1857590675354</v>
+        <v>4.18575954437256</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.02180099487305</v>
+        <v>4.02180051803589</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.33042764663696</v>
+        <v>4.33042812347412</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.46545267105103</v>
+        <v>4.46545314788818</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.37865114212036</v>
+        <v>4.37865161895752</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.42687463760376</v>
+        <v>4.4268741607666</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.47509717941284</v>
+        <v>4.47509670257568</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1582" t="n">
-        <v>4.5329647064209</v>
+        <v>4.53296518325806</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1583" t="n">
-        <v>4.49438667297363</v>
+        <v>4.49438619613647</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.49438667297363</v>
+        <v>4.49438619613647</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1587" t="n">
-        <v>4.44616317749023</v>
+        <v>4.44616365432739</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1589" t="n">
-        <v>4.37865114212036</v>
+        <v>4.37865161895752</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.34971761703491</v>
+        <v>4.34971714019775</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.5329647064209</v>
+        <v>4.53296518325806</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.49438667297363</v>
+        <v>4.49438619613647</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.5329647064209</v>
+        <v>4.53296518325806</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.64869976043701</v>
+        <v>4.64870023727417</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1600" t="n">
-        <v>4.61012172698975</v>
+        <v>4.6101222038269</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1601" t="n">
-        <v>4.57154321670532</v>
+        <v>4.57154273986816</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.49438667297363</v>
+        <v>4.49438619613647</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1603" t="n">
-        <v>4.49438667297363</v>
+        <v>4.49438619613647</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>4.49438667297363</v>
+        <v>4.49438619613647</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1606" t="n">
-        <v>4.40758562088013</v>
+        <v>4.40758514404297</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.44616317749023</v>
+        <v>4.44616365432739</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.40758562088013</v>
+        <v>4.40758514404297</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.3690071105957</v>
+        <v>4.36900663375854</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.40758562088013</v>
+        <v>4.40758514404297</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1613" t="n">
-        <v>4.34971761703491</v>
+        <v>4.34971714019775</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1615" t="n">
-        <v>4.11824655532837</v>
+        <v>4.11824703216553</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>4.15682554244995</v>
+        <v>4.15682506561279</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.78372478485107</v>
+        <v>4.78372430801392</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1632" t="n">
-        <v>5.0151948928833</v>
+        <v>5.01519536972046</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1633" t="n">
-        <v>5.45884704589844</v>
+        <v>5.45884656906128</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>5.28524446487427</v>
+        <v>5.28524398803711</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1638" t="n">
-        <v>5.42026805877686</v>
+        <v>5.42026901245117</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1640" t="n">
-        <v>4.86088132858276</v>
+        <v>4.86088180541992</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1641" t="n">
-        <v>4.84159183502197</v>
+        <v>4.84159231185913</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.78372478485107</v>
+        <v>4.78372430801392</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.73550128936768</v>
+        <v>4.73550176620483</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1647" t="n">
-        <v>4.87276268005371</v>
+        <v>4.87276220321655</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.96100187301636</v>
+        <v>4.9610013961792</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1649" t="n">
-        <v>5.13748025894165</v>
+        <v>5.13747978210449</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1654" t="n">
-        <v>4.96100187301636</v>
+        <v>4.9610013961792</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.00021886825562</v>
+        <v>5.00021934509277</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1659" t="n">
-        <v>5.00021886825562</v>
+        <v>5.00021934509277</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1660" t="n">
-        <v>4.81393623352051</v>
+        <v>4.81393671035767</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1661" t="n">
-        <v>4.79432725906372</v>
+        <v>4.79432773590088</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1663" t="n">
-        <v>4.67667579650879</v>
+        <v>4.67667531967163</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1666" t="n">
-        <v>4.81393623352051</v>
+        <v>4.81393671035767</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1668" t="n">
-        <v>4.79432725906372</v>
+        <v>4.79432773590088</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1672" t="n">
-        <v>4.72569704055786</v>
+        <v>4.72569751739502</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1673" t="n">
-        <v>4.80413246154785</v>
+        <v>4.80413198471069</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>4.80413246154785</v>
+        <v>4.80413198471069</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>4.80413246154785</v>
+        <v>4.80413198471069</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1677" t="n">
-        <v>4.79432725906372</v>
+        <v>4.79432773590088</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>4.81393623352051</v>
+        <v>4.81393671035767</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1680" t="n">
-        <v>4.92178392410278</v>
+        <v>4.92178440093994</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1682" t="n">
-        <v>4.80413246154785</v>
+        <v>4.80413198471069</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>4.83354520797729</v>
+        <v>4.83354473114014</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1689" t="n">
-        <v>4.72569704055786</v>
+        <v>4.72569751739502</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1690" t="n">
-        <v>4.66687107086182</v>
+        <v>4.66687154769897</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1705" t="n">
-        <v>4.72569704055786</v>
+        <v>4.72569751739502</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1709" t="n">
-        <v>4.74530649185181</v>
+        <v>4.74530601501465</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1716" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1717" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1718" t="n">
-        <v>4.5982403755188</v>
+        <v>4.59824085235596</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1721" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1722" t="n">
-        <v>4.5982403755188</v>
+        <v>4.59824085235596</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1726" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1728" t="n">
-        <v>4.54921913146973</v>
+        <v>4.54921865463257</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1732" t="n">
-        <v>4.66687107086182</v>
+        <v>4.66687154769897</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1733" t="n">
-        <v>4.5982403755188</v>
+        <v>4.59824085235596</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1756" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1757" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.38254451751709</v>
+        <v>4.38254499435425</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1770" t="n">
-        <v>4.38254451751709</v>
+        <v>4.38254499435425</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1771" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.26489305496216</v>
+        <v>4.264892578125</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.26489305496216</v>
+        <v>4.264892578125</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="n">
-        <v>4.21587133407593</v>
+        <v>4.21587085723877</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1777" t="n">
-        <v>4.26489305496216</v>
+        <v>4.264892578125</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>4.25508832931519</v>
+        <v>4.25508880615234</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.1374363899231</v>
+        <v>4.13743591308594</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1789" t="n">
-        <v>4.33352375030518</v>
+        <v>4.33352327346802</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1792" t="n">
-        <v>4.45117521286011</v>
+        <v>4.45117568969727</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1803" t="n">
-        <v>4.5982403755188</v>
+        <v>4.59824085235596</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1805" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.37274074554443</v>
+        <v>4.37274026870728</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.54921913146973</v>
+        <v>4.54921865463257</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1821" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.51000118255615</v>
+        <v>4.51000165939331</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.79432725906372</v>
+        <v>4.79432773590088</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1829" t="n">
-        <v>4.81393623352051</v>
+        <v>4.81393671035767</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1830" t="n">
-        <v>4.81393623352051</v>
+        <v>4.81393671035767</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.74530649185181</v>
+        <v>4.74530601501465</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>4.25</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.16684913635254</v>
+        <v>4.1668496131897</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.19626235961914</v>
+        <v>4.1962628364563</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.33352375030518</v>
+        <v>4.33352327346802</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.26489305496216</v>
+        <v>4.264892578125</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.33352375030518</v>
+        <v>4.33352327346802</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1870" t="n">
-        <v>4.33352375030518</v>
+        <v>4.33352327346802</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1871" t="n">
-        <v>4.38254451751709</v>
+        <v>4.38254499435425</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.32371854782104</v>
+        <v>4.3237190246582</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.45117521286011</v>
+        <v>4.45117568969727</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.45117521286011</v>
+        <v>4.45117568969727</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.37274074554443</v>
+        <v>4.37274026870728</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.33352375030518</v>
+        <v>4.33352327346802</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>4.09999990463257</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>435</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>
